--- a/TPB.xlsx
+++ b/TPB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D312F7C-E36B-487E-B328-A23C1DF419F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A74055A-2814-42DB-A26B-3D092BDA28C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="1950" windowWidth="38175" windowHeight="15240" xr2:uid="{C81D1CBC-96B8-4154-B447-A9A1A7A2C710}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{C81D1CBC-96B8-4154-B447-A9A1A7A2C710}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="73">
   <si>
     <t>Turning Point Brands</t>
   </si>
@@ -230,6 +230,33 @@
   <si>
     <t>B2B distrubution soultions</t>
   </si>
+  <si>
+    <t>Alp nicotine pouches partnership with Tucker Carlson</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
 </sst>
 </file>
 
@@ -239,13 +266,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -434,37 +467,42 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -801,7 +839,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A36FB96-90CB-4784-9B70-ACD36F5D1097}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="2" customWidth="1"/>
@@ -826,7 +864,7 @@
         <v>2</v>
       </c>
       <c r="I3" s="3">
-        <v>69.63</v>
+        <v>90.75</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -837,10 +875,10 @@
         <v>1</v>
       </c>
       <c r="I4" s="3">
-        <v>17.697006999999999</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>10</v>
+        <v>19.367533999999999</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -852,7 +890,7 @@
       </c>
       <c r="I5" s="3">
         <f>I3*I4</f>
-        <v>1232.2425974099999</v>
+        <v>1757.6037105</v>
       </c>
       <c r="J5" s="5"/>
     </row>
@@ -861,10 +899,10 @@
         <v>4</v>
       </c>
       <c r="I6" s="3">
-        <v>33.557000000000002</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>10</v>
+        <v>192.43899999999999</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -882,11 +920,10 @@
         <v>5</v>
       </c>
       <c r="I7" s="3">
-        <f>248.282+0</f>
-        <v>248.28200000000001</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>10</v>
+        <v>293.88499999999999</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -905,7 +942,7 @@
       </c>
       <c r="I8" s="3">
         <f>I5-I6+I7</f>
-        <v>1446.9675974099998</v>
+        <v>1859.0497104999999</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -946,6 +983,11 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B17" s="25" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -996,6 +1038,30 @@
       <c r="J2" s="5" t="s">
         <v>18</v>
       </c>
+      <c r="K2" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="M2" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="N2" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="O2" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="P2" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q2" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="R2" s="26" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="3" spans="1:56" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -1021,9 +1087,14 @@
         <v>97.634</v>
       </c>
       <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
+      <c r="K3" s="3">
+        <v>100.488</v>
+      </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
+      <c r="O3" s="2">
+        <v>116.15300000000001</v>
+      </c>
     </row>
     <row r="4" spans="1:56" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
@@ -1049,9 +1120,14 @@
         <v>7.9829999999999997</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+      <c r="K4" s="3">
+        <v>5.9480000000000004</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
+      <c r="O4" s="2">
+        <v>8.125</v>
+      </c>
     </row>
     <row r="5" spans="1:56" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
@@ -1077,11 +1153,15 @@
         <v>49.323999999999998</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
+      <c r="K5" s="3">
+        <v>47.265000000000001</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="O5" s="3">
+        <v>36.668999999999997</v>
+      </c>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
@@ -1142,11 +1222,15 @@
         <v>41.38</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
+      <c r="K6" s="3">
+        <v>59.170999999999999</v>
+      </c>
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+      <c r="O6" s="3">
+        <v>87.608999999999995</v>
+      </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
@@ -1213,11 +1297,15 @@
         <v>14.913</v>
       </c>
       <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="K7" s="27">
+        <v>0</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
+      <c r="O7" s="27">
+        <v>0</v>
+      </c>
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
@@ -1284,11 +1372,15 @@
         <v>105.617</v>
       </c>
       <c r="J8" s="22"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
+      <c r="K8" s="22">
+        <v>106.43600000000001</v>
+      </c>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="22">
+        <v>124.27800000000001</v>
+      </c>
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
@@ -1355,11 +1447,15 @@
         <v>51.917999999999999</v>
       </c>
       <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="K9" s="3">
+        <v>46.826000000000001</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
+      <c r="O9" s="3">
+        <v>55.982999999999997</v>
+      </c>
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
@@ -1426,11 +1522,15 @@
         <v>27.327000000000002</v>
       </c>
       <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="K10" s="3">
+        <v>25.565000000000001</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
+      <c r="O10" s="3">
+        <v>20.945</v>
+      </c>
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
@@ -1497,11 +1597,15 @@
         <v>23.071000000000002</v>
       </c>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <v>34.045000000000002</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
+      <c r="O11" s="3">
+        <v>47.35</v>
+      </c>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
@@ -1568,11 +1672,15 @@
         <v>3.3010000000000002</v>
       </c>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="K12" s="27">
+        <v>0</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
+      <c r="O12" s="27">
+        <v>0</v>
+      </c>
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
@@ -1620,7 +1728,7 @@
         <v>21</v>
       </c>
       <c r="C13" s="3">
-        <f t="shared" ref="C13:J13" si="0">+C8-C9</f>
+        <f t="shared" ref="C13:R13" si="0">+C8-C9</f>
         <v>48.617000000000004</v>
       </c>
       <c r="D13" s="3">
@@ -1651,14 +1759,38 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
+      <c r="K13" s="3">
+        <f t="shared" si="0"/>
+        <v>59.610000000000007</v>
+      </c>
+      <c r="L13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <f t="shared" si="0"/>
+        <v>68.295000000000016</v>
+      </c>
+      <c r="P13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
       <c r="U13" s="3"/>
@@ -1722,11 +1854,15 @@
         <v>33.159999999999997</v>
       </c>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="K14" s="3">
+        <v>36.420999999999999</v>
+      </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
+      <c r="O14" s="3">
+        <v>55.811</v>
+      </c>
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
@@ -1793,11 +1929,15 @@
         <v>0</v>
       </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
+      <c r="O15" s="3">
+        <v>0</v>
+      </c>
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
@@ -1845,7 +1985,7 @@
         <v>26</v>
       </c>
       <c r="C16" s="3">
-        <f t="shared" ref="C16:J16" si="1">+C13-SUM(C14:C15)</f>
+        <f t="shared" ref="C16:Q16" si="1">+C13-SUM(C14:C15)</f>
         <v>17.842000000000006</v>
       </c>
       <c r="D16" s="3">
@@ -1876,13 +2016,34 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
+      <c r="K16" s="3">
+        <f t="shared" si="1"/>
+        <v>23.189000000000007</v>
+      </c>
+      <c r="L16" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N16" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O16" s="3">
+        <f t="shared" si="1"/>
+        <v>12.484000000000016</v>
+      </c>
+      <c r="P16" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
@@ -1947,11 +2108,16 @@
         <v>3.7730000000000001</v>
       </c>
       <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
+      <c r="K17" s="3">
+        <v>4.4139999999999997</v>
+      </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
+      <c r="O17" s="3">
+        <f>4.423+0.063</f>
+        <v>4.4859999999999998</v>
+      </c>
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
@@ -2018,11 +2184,15 @@
         <v>-0.20300000000000001</v>
       </c>
       <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
+      <c r="K18" s="3">
+        <v>-0.14099999999999999</v>
+      </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
+      <c r="O18" s="3">
+        <v>-0.151</v>
+      </c>
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
@@ -2089,11 +2259,16 @@
         <v>0</v>
       </c>
       <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
+      <c r="K19" s="3">
+        <f>0.15-1.235</f>
+        <v>-1.0850000000000002</v>
+      </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
+      <c r="O19" s="3">
+        <v>2.9830000000000001</v>
+      </c>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
@@ -2169,16 +2344,37 @@
         <v>16.969000000000008</v>
       </c>
       <c r="J20" s="3">
-        <f t="shared" ref="J20" si="3">+J16-J17-J18+J19</f>
+        <f t="shared" ref="J20:Q20" si="3">+J16-J17-J18+J19</f>
         <v>0</v>
       </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
+      <c r="K20" s="3">
+        <f t="shared" si="3"/>
+        <v>17.831000000000003</v>
+      </c>
+      <c r="L20" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
+        <f t="shared" si="3"/>
+        <v>11.132000000000017</v>
+      </c>
+      <c r="P20" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
@@ -2243,11 +2439,15 @@
         <v>4.601</v>
       </c>
       <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
+      <c r="K21" s="3">
+        <v>2.04</v>
+      </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
+      <c r="O21" s="3">
+        <v>-2.81</v>
+      </c>
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
@@ -2323,15 +2523,33 @@
         <v>12.368000000000009</v>
       </c>
       <c r="J22" s="3">
-        <f t="shared" ref="J22" si="5">+J20-J21</f>
+        <f t="shared" ref="J22:P22" si="5">+J20-J21</f>
         <v>0</v>
       </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-      <c r="P22" s="3"/>
+      <c r="K22" s="3">
+        <f t="shared" si="5"/>
+        <v>15.791000000000004</v>
+      </c>
+      <c r="L22" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="3">
+        <f t="shared" si="5"/>
+        <v>13.942000000000018</v>
+      </c>
+      <c r="P22" s="3">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
@@ -2397,11 +2615,15 @@
         <v>-1.6E-2</v>
       </c>
       <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
+      <c r="K23" s="3">
+        <v>1.3959999999999999</v>
+      </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
+      <c r="O23" s="3">
+        <v>2.2749999999999999</v>
+      </c>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
@@ -2477,16 +2699,37 @@
         <v>12.384000000000009</v>
       </c>
       <c r="J24" s="3">
-        <f t="shared" ref="J24" si="7">+J22-J23</f>
+        <f t="shared" ref="J24:Q24" si="7">+J22-J23</f>
         <v>0</v>
       </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-      <c r="P24" s="3"/>
-      <c r="Q24" s="3"/>
+      <c r="K24" s="3">
+        <f t="shared" si="7"/>
+        <v>14.395000000000003</v>
+      </c>
+      <c r="L24" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <f t="shared" si="7"/>
+        <v>11.667000000000018</v>
+      </c>
+      <c r="P24" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
@@ -2616,16 +2859,37 @@
         <v>0.69875874964840656</v>
       </c>
       <c r="J26" s="23" t="e">
-        <f t="shared" ref="J26" si="9">+J24/J27</f>
+        <f t="shared" ref="J26:Q26" si="9">+J24/J27</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
+      <c r="K26" s="23">
+        <f t="shared" si="9"/>
+        <v>0.80892404784806837</v>
+      </c>
+      <c r="L26" s="23" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M26" s="23" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N26" s="23" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O26" s="23">
+        <f t="shared" si="9"/>
+        <v>0.60720119697795316</v>
+      </c>
+      <c r="P26" s="23" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q26" s="23" t="e">
+        <f t="shared" si="9"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
@@ -2690,11 +2954,15 @@
         <v>17.722854999999999</v>
       </c>
       <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
+      <c r="K27" s="3">
+        <v>17.795242999999999</v>
+      </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
+      <c r="O27" s="3">
+        <v>19.214389000000001</v>
+      </c>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
       <c r="R27" s="3"/>
